--- a/downloads/exercises/intermedio-m02-m02-l08-practice-01.xlsx
+++ b/downloads/exercises/intermedio-m02-m02-l08-practice-01.xlsx
@@ -497,7 +497,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="4" t="str">
-        <x:v>2. Modifica Columnas a 10 y Filas a 1 para crear una secuencia horizontal.</x:v>
+        <x:v>2. Antes de cambiar la orientación, borra sólo la fórmula origen de D5 y escribe en N5 =SECUENCIA(B5;B6;B7;B8) (en inglés, =SEQUENCE(B5,B6,B7,B8)); conserva B5:B8 y las anotaciones. Modifica Columnas a 10 y Filas a 1 para crear una secuencia horizontal.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
